--- a/data/processed/positivacao/2024-05_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2024-05_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25621,7 +25621,7 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B973" t="inlineStr"/>
@@ -36973,7 +36973,7 @@
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr"/>
@@ -65397,7 +65397,7 @@
     <row r="2504">
       <c r="A2504" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2504" t="inlineStr"/>
@@ -67016,12 +67016,12 @@
       <c r="A2567" t="inlineStr"/>
       <c r="B2567" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 6 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 4.200,55
+          <t>Vendedor 1 - VENDEDOR 01: positivou 6 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 4.200,55
 Vendedor 18 - LOJA: positivou 142 cliente(s), não positivou 729 cliente(s) - Total vendido: R$ 58.075,29
-Vendedor 3 - FERNANDA: positivou 95 cliente(s), não positivou 341 cliente(s) - Total vendido: R$ 139.799,93
-Vendedor 4 - DANIELA: positivou 57 cliente(s), não positivou 587 cliente(s) - Total vendido: R$ 31.719,00
+Vendedor 3 - VENDEDOR 03: positivou 95 cliente(s), não positivou 341 cliente(s) - Total vendido: R$ 139.799,93
+Vendedor 4 - VENDEDOR 04: positivou 57 cliente(s), não positivou 587 cliente(s) - Total vendido: R$ 31.719,00
 Vendedor 5 - SITE: positivou 2 cliente(s), não positivou 446 cliente(s) - Total vendido: R$ 259,00
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2567" t="inlineStr"/>
